--- a/data/trans_orig/P19-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P19-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 6 meses han ido al dentista en 2007</t>
+          <t>Población según si en los últimos 6 meses han ido al dentista en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>104615</t>
+          <t>105145</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>141806</t>
+          <t>141337</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>167868</t>
+          <t>169236</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>208212</t>
+          <t>208606</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>281314</t>
+          <t>284888</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>339844</t>
+          <t>341998</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,57%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>352258</t>
+          <t>352727</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>389449</t>
+          <t>388919</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>259277</t>
+          <t>258883</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>299621</t>
+          <t>298253</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>621709</t>
+          <t>619555</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>680239</t>
+          <t>676665</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,37%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>176932</t>
+          <t>176533</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>225817</t>
+          <t>224933</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>185651</t>
+          <t>186415</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>233744</t>
+          <t>231749</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>377024</t>
+          <t>372689</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>445097</t>
+          <t>446755</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,83%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>509672</t>
+          <t>510556</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>558557</t>
+          <t>558956</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>391750</t>
+          <t>393745</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>439843</t>
+          <t>439079</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>915885</t>
+          <t>914227</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>983958</t>
+          <t>988293</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,62%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>145453</t>
+          <t>142214</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>189831</t>
+          <t>187146</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>203791</t>
+          <t>203760</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>252135</t>
+          <t>252004</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>363768</t>
+          <t>360852</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>429874</t>
+          <t>426257</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,09%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>448837</t>
+          <t>451522</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>493215</t>
+          <t>496454</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>437609</t>
+          <t>437740</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>485953</t>
+          <t>485984</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>898538</t>
+          <t>902155</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>964644</t>
+          <t>967560</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,84%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>120828</t>
+          <t>120575</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>162298</t>
+          <t>167307</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>172199</t>
+          <t>170837</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>215292</t>
+          <t>215618</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>303258</t>
+          <t>305392</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>364419</t>
+          <t>367181</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,51%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>355937</t>
+          <t>350928</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>397407</t>
+          <t>397660</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>300350</t>
+          <t>300024</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>343443</t>
+          <t>344805</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>669458</t>
+          <t>666696</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>730619</t>
+          <t>728485</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,46%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>78686</t>
+          <t>78718</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>112082</t>
+          <t>112623</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>102222</t>
+          <t>101825</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>138936</t>
+          <t>139007</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>191624</t>
+          <t>191130</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>239310</t>
+          <t>241661</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,6%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>274628</t>
+          <t>274087</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>308024</t>
+          <t>307992</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>264125</t>
+          <t>264054</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>300839</t>
+          <t>301236</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>550461</t>
+          <t>548110</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>598147</t>
+          <t>598641</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,8%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49895</t>
+          <t>48387</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76755</t>
+          <t>75504</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>60090</t>
+          <t>61052</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>90703</t>
+          <t>89115</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>117154</t>
+          <t>118850</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>155705</t>
+          <t>156420</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>215828</t>
+          <t>217079</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>242688</t>
+          <t>244196</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>252231</t>
+          <t>253819</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>282844</t>
+          <t>281882</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>479812</t>
+          <t>479097</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>518363</t>
+          <t>516667</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,3%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19651</t>
+          <t>19714</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38843</t>
+          <t>40027</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34403</t>
+          <t>34276</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61025</t>
+          <t>62944</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60271</t>
+          <t>59510</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>93470</t>
+          <t>92090</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,93%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>171040</t>
+          <t>169856</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>190232</t>
+          <t>190169</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>272883</t>
+          <t>270964</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>299505</t>
+          <t>299632</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>450321</t>
+          <t>451701</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>483520</t>
+          <t>484281</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,06%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>761136</t>
+          <t>765770</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>862782</t>
+          <t>869320</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1006886</t>
+          <t>1006060</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1110122</t>
+          <t>1115428</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1798612</t>
+          <t>1794572</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1942870</t>
+          <t>1949930</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2412849</t>
+          <t>2406311</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2514495</t>
+          <t>2509861</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2268150</t>
+          <t>2262844</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2371386</t>
+          <t>2372212</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4711034</t>
+          <t>4703974</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4855292</t>
+          <t>4859332</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>73,03%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 6 meses han ido al dentista en 2012</t>
+          <t>Población según si en los últimos 6 meses han ido al dentista en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>119099</t>
+          <t>119275</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>159041</t>
+          <t>158985</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>143463</t>
+          <t>143132</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>184840</t>
+          <t>182757</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>272667</t>
+          <t>272836</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>329619</t>
+          <t>327752</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,06%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>295105</t>
+          <t>295161</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>335047</t>
+          <t>334871</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>245390</t>
+          <t>247473</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286767</t>
+          <t>287098</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>554757</t>
+          <t>556624</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>611709</t>
+          <t>611540</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,15%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>177900</t>
+          <t>177744</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>228987</t>
+          <t>225239</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>180286</t>
+          <t>184683</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>228551</t>
+          <t>233129</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>372554</t>
+          <t>375809</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>440314</t>
+          <t>440636</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,99%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>456950</t>
+          <t>460698</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>508037</t>
+          <t>508193</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>381704</t>
+          <t>377126</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>429969</t>
+          <t>425572</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>855879</t>
+          <t>855557</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>923639</t>
+          <t>920384</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>71,01%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>155077</t>
+          <t>153770</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>201262</t>
+          <t>201312</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>219852</t>
+          <t>219294</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>269845</t>
+          <t>269724</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>387641</t>
+          <t>382965</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>456989</t>
+          <t>451903</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,45%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>480601</t>
+          <t>480551</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>526786</t>
+          <t>528093</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>441005</t>
+          <t>441126</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>490998</t>
+          <t>491556</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>935723</t>
+          <t>940809</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1005071</t>
+          <t>1009747</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,5%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>135525</t>
+          <t>138891</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>181700</t>
+          <t>183182</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>172397</t>
+          <t>175113</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>224387</t>
+          <t>224045</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>328265</t>
+          <t>331662</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>394742</t>
+          <t>395738</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,18%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>432917</t>
+          <t>431435</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>479092</t>
+          <t>475726</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>390848</t>
+          <t>391190</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>442838</t>
+          <t>440122</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>835109</t>
+          <t>834113</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>901586</t>
+          <t>898189</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,03%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>72297</t>
+          <t>71771</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>107557</t>
+          <t>107783</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>102813</t>
+          <t>104385</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>142379</t>
+          <t>145256</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>187371</t>
+          <t>187404</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>240630</t>
+          <t>239722</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,37%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>320509</t>
+          <t>320283</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>355769</t>
+          <t>356295</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>305421</t>
+          <t>302544</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>344987</t>
+          <t>343415</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>635236</t>
+          <t>636144</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>688495</t>
+          <t>688462</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,6%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42216</t>
+          <t>41833</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71509</t>
+          <t>70837</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>76784</t>
+          <t>77043</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>112335</t>
+          <t>113001</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>125910</t>
+          <t>128291</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>172122</t>
+          <t>172546</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>238277</t>
+          <t>238949</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>267570</t>
+          <t>267953</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>241661</t>
+          <t>240995</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277212</t>
+          <t>276953</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>491660</t>
+          <t>491236</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>537872</t>
+          <t>535491</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>80,67%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13842</t>
+          <t>14944</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32492</t>
+          <t>32995</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37501</t>
+          <t>37581</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>65101</t>
+          <t>65078</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>56653</t>
+          <t>56175</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>89407</t>
+          <t>89943</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>217359</t>
+          <t>216856</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>236009</t>
+          <t>234907</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>323878</t>
+          <t>323901</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>351478</t>
+          <t>351398</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>549423</t>
+          <t>548887</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>582177</t>
+          <t>582655</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,21%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>793371</t>
+          <t>795892</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>893185</t>
+          <t>897514</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1026159</t>
+          <t>1018088</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1139075</t>
+          <t>1129440</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1849388</t>
+          <t>1844792</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2002245</t>
+          <t>1998460</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,62%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2531081</t>
+          <t>2526752</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2630895</t>
+          <t>2628374</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2418270</t>
+          <t>2427905</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2531186</t>
+          <t>2539257</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4979365</t>
+          <t>4983150</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5132222</t>
+          <t>5136818</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,58%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 6 meses han ido al dentista en 2016</t>
+          <t>Población según si en los últimos 6 meses han ido al dentista en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>141936</t>
+          <t>141688</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>184919</t>
+          <t>181901</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,47 +6706,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>43,37%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>174433</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>156853</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>193314</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>44,08%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>174433</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>155056</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>194222</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>44,08%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>310582</t>
+          <t>307005</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>365103</t>
+          <t>364465</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,71%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>234544</t>
+          <t>237562</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>277527</t>
+          <t>277775</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,47 +6819,47 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>56,63%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>66,22%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>221322</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>202441</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>238902</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
           <t>55,92%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>66,16%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>221322</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>201533</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>240699</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>55,92%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>450115</t>
+          <t>450753</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>504636</t>
+          <t>508213</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>62,34%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>182771</t>
+          <t>184024</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>231031</t>
+          <t>228206</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>216351</t>
+          <t>218004</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>260472</t>
+          <t>262877</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>411829</t>
+          <t>411262</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>478406</t>
+          <t>476440</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,28%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>359465</t>
+          <t>362290</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>407725</t>
+          <t>406472</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>303072</t>
+          <t>300667</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>347193</t>
+          <t>345540</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>675634</t>
+          <t>677600</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>742211</t>
+          <t>742778</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>64,36%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>167830</t>
+          <t>168485</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>217101</t>
+          <t>214919</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>213110</t>
+          <t>214160</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>262553</t>
+          <t>262071</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>400250</t>
+          <t>392893</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>468633</t>
+          <t>462883</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>34,79%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>451996</t>
+          <t>454178</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>501267</t>
+          <t>500612</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>398833</t>
+          <t>399315</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>448276</t>
+          <t>447226</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>861850</t>
+          <t>867600</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>930233</t>
+          <t>937590</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>70,47%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>170278</t>
+          <t>171272</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>220802</t>
+          <t>217897</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>208090</t>
+          <t>210273</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>260108</t>
+          <t>260717</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>393859</t>
+          <t>394747</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>465106</t>
+          <t>465203</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,92%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>425246</t>
+          <t>428151</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>475770</t>
+          <t>474776</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>388969</t>
+          <t>388360</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>440987</t>
+          <t>438804</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>830019</t>
+          <t>829922</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>901266</t>
+          <t>900378</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,52%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>110601</t>
+          <t>109642</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>154147</t>
+          <t>152061</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>133591</t>
+          <t>133711</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>177410</t>
+          <t>179256</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>257094</t>
+          <t>257154</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>318700</t>
+          <t>315457</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>323771</t>
+          <t>325857</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>367317</t>
+          <t>368276</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>319439</t>
+          <t>317593</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>363258</t>
+          <t>363138</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>656067</t>
+          <t>659310</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>717673</t>
+          <t>717613</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,62%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51419</t>
+          <t>51793</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80959</t>
+          <t>82069</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>96401</t>
+          <t>96354</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>130743</t>
+          <t>133710</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>155763</t>
+          <t>157127</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>204698</t>
+          <t>205551</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,87%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253371</t>
+          <t>252261</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>282911</t>
+          <t>282537</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>247019</t>
+          <t>244052</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>281361</t>
+          <t>281408</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>507394</t>
+          <t>506541</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>556329</t>
+          <t>554965</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>77,93%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26103</t>
+          <t>26479</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45200</t>
+          <t>46262</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53036</t>
+          <t>53664</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>87993</t>
+          <t>88207</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>84266</t>
+          <t>86613</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>126476</t>
+          <t>125988</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,17%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>211798</t>
+          <t>210736</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>230895</t>
+          <t>230519</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>312176</t>
+          <t>311962</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>347133</t>
+          <t>346505</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>530691</t>
+          <t>531179</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>572901</t>
+          <t>570554</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>86,82%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>927665</t>
+          <t>934257</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1038411</t>
+          <t>1035721</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1165881</t>
+          <t>1168344</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1279347</t>
+          <t>1281496</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2120052</t>
+          <t>2131619</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2285927</t>
+          <t>2290065</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,0%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2355939</t>
+          <t>2358629</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2466685</t>
+          <t>2460093</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2265195</t>
+          <t>2263046</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2378661</t>
+          <t>2376198</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4652965</t>
+          <t>4648827</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4818840</t>
+          <t>4807273</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,28%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 6 meses han ido al dentista en 2023</t>
+          <t>Población según si en los últimos 6 meses han ido al dentista en 2023 (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>81129</t>
+          <t>84285</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>145756</t>
+          <t>145853</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>79833</t>
+          <t>79934</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>123026</t>
+          <t>122147</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>174882</t>
+          <t>175642</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>248861</t>
+          <t>253459</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,93%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>248726</t>
+          <t>248629</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>313353</t>
+          <t>310197</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>187946</t>
+          <t>188825</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>231139</t>
+          <t>231038</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>456593</t>
+          <t>451995</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>530572</t>
+          <t>529812</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,1%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>105422</t>
+          <t>108519</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>159167</t>
+          <t>153498</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>100155</t>
+          <t>96531</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>185640</t>
+          <t>184686</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>216903</t>
+          <t>212455</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>319066</t>
+          <t>320732</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,46%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>262759</t>
+          <t>268428</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>316504</t>
+          <t>313407</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>323159</t>
+          <t>324113</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>408644</t>
+          <t>412268</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>611659</t>
+          <t>609993</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>713822</t>
+          <t>718270</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>77,17%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>127155</t>
+          <t>128607</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>171971</t>
+          <t>171697</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>192788</t>
+          <t>193505</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>231134</t>
+          <t>230848</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>331873</t>
+          <t>329916</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>387457</t>
+          <t>388145</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,16%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>362008</t>
+          <t>362282</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>406824</t>
+          <t>405372</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>308292</t>
+          <t>308578</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>346638</t>
+          <t>345921</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>685948</t>
+          <t>685260</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>741532</t>
+          <t>743489</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>69,26%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84478</t>
+          <t>82317</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>274564</t>
+          <t>275421</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>243909</t>
+          <t>245854</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>339922</t>
+          <t>340948</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>287235</t>
+          <t>289318</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>569973</t>
+          <t>568572</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,7%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>611140</t>
+          <t>610283</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>801226</t>
+          <t>803387</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>367055</t>
+          <t>366029</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>463068</t>
+          <t>461123</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1022708</t>
+          <t>1024109</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1305446</t>
+          <t>1303363</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>81,83%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>124591</t>
+          <t>124382</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>163791</t>
+          <t>165950</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>168837</t>
+          <t>168880</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>203530</t>
+          <t>199443</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>304194</t>
+          <t>305867</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>356377</t>
+          <t>352947</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,17%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>394663</t>
+          <t>392504</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>433863</t>
+          <t>434072</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>335129</t>
+          <t>339216</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>369822</t>
+          <t>369779</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>740736</t>
+          <t>744166</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>792919</t>
+          <t>791246</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,12%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>84385</t>
+          <t>83495</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>111934</t>
+          <t>111289</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>46121</t>
+          <t>41146</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>162540</t>
+          <t>162682</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>107471</t>
+          <t>102907</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>262132</t>
+          <t>261379</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,94%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>250699</t>
+          <t>251344</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>278248</t>
+          <t>279138</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>445082</t>
+          <t>444940</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>561501</t>
+          <t>566476</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>708123</t>
+          <t>708876</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>862784</t>
+          <t>867348</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,39%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32669</t>
+          <t>32706</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50634</t>
+          <t>51342</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47350</t>
+          <t>48322</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67571</t>
+          <t>69260</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>85546</t>
+          <t>85855</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>114819</t>
+          <t>113478</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,29%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>228720</t>
+          <t>228012</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>246685</t>
+          <t>246648</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>349788</t>
+          <t>348099</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>370009</t>
+          <t>369037</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>581894</t>
+          <t>583235</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>611167</t>
+          <t>610858</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,68%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>650025</t>
+          <t>669893</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>952093</t>
+          <t>947806</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>878391</t>
+          <t>884215</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1189142</t>
+          <t>1187018</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1715635</t>
+          <t>1673995</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2097718</t>
+          <t>2093062</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,62%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2484439</t>
+          <t>2488726</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2786507</t>
+          <t>2766639</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2440672</t>
+          <t>2442796</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2751423</t>
+          <t>2745599</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4968628</t>
+          <t>4973284</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5350711</t>
+          <t>5392351</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>76,31%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P19-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>105145</t>
+          <t>103749</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>141337</t>
+          <t>141012</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>169236</t>
+          <t>169145</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>208606</t>
+          <t>210620</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>284888</t>
+          <t>284023</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>341998</t>
+          <t>339248</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,28%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>352727</t>
+          <t>353052</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>388919</t>
+          <t>390315</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>258883</t>
+          <t>256869</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>298253</t>
+          <t>298344</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>619555</t>
+          <t>622305</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>676665</t>
+          <t>677530</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,46%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>176533</t>
+          <t>174047</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>224933</t>
+          <t>223794</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>186415</t>
+          <t>185001</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>231749</t>
+          <t>236272</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>372689</t>
+          <t>375183</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>446755</t>
+          <t>443339</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,57%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>510556</t>
+          <t>511695</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>558956</t>
+          <t>561442</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>393745</t>
+          <t>389222</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>439079</t>
+          <t>440493</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>914227</t>
+          <t>917643</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>988293</t>
+          <t>985799</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,43%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>142214</t>
+          <t>144658</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>187146</t>
+          <t>191241</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>203760</t>
+          <t>202412</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>252004</t>
+          <t>253402</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>360852</t>
+          <t>359973</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>426257</t>
+          <t>426505</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,11%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>451522</t>
+          <t>447427</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>496454</t>
+          <t>494010</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>437740</t>
+          <t>436342</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>485984</t>
+          <t>487332</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>902155</t>
+          <t>901907</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>967560</t>
+          <t>968439</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,9%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>120575</t>
+          <t>120479</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>167307</t>
+          <t>162685</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>170837</t>
+          <t>170379</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>215618</t>
+          <t>215922</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>305392</t>
+          <t>302490</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>367181</t>
+          <t>365268</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,33%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>350928</t>
+          <t>355550</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>397660</t>
+          <t>397756</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>300024</t>
+          <t>299720</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>344805</t>
+          <t>345263</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>666696</t>
+          <t>668609</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>728485</t>
+          <t>731387</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,74%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>78718</t>
+          <t>77399</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>112623</t>
+          <t>111206</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>101825</t>
+          <t>102249</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>139007</t>
+          <t>138229</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>191130</t>
+          <t>190518</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>241661</t>
+          <t>239297</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,3%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>274087</t>
+          <t>275504</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>307992</t>
+          <t>309311</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>264054</t>
+          <t>264832</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>301236</t>
+          <t>300812</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>548110</t>
+          <t>550474</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>598641</t>
+          <t>599253</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,88%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48387</t>
+          <t>49194</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>75504</t>
+          <t>76823</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>61052</t>
+          <t>62428</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>89115</t>
+          <t>90618</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>118850</t>
+          <t>116613</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>156420</t>
+          <t>157930</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,85%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>217079</t>
+          <t>215760</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>244196</t>
+          <t>243389</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>253819</t>
+          <t>252316</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>281882</t>
+          <t>280506</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>479097</t>
+          <t>477587</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>516667</t>
+          <t>518904</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,65%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19714</t>
+          <t>20245</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40027</t>
+          <t>38696</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34276</t>
+          <t>34215</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62944</t>
+          <t>61329</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>59510</t>
+          <t>59404</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>92090</t>
+          <t>92845</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,07%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>169856</t>
+          <t>171187</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>190169</t>
+          <t>189638</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>270964</t>
+          <t>272579</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>299632</t>
+          <t>299693</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>451701</t>
+          <t>450946</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>484281</t>
+          <t>484387</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,08%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>765770</t>
+          <t>767116</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>869320</t>
+          <t>869016</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1006060</t>
+          <t>1007614</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1115428</t>
+          <t>1115681</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1794572</t>
+          <t>1806499</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1949930</t>
+          <t>1946168</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,25%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2406311</t>
+          <t>2406615</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2509861</t>
+          <t>2508515</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2262844</t>
+          <t>2262591</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2372212</t>
+          <t>2370658</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4703974</t>
+          <t>4707736</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4859332</t>
+          <t>4847405</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>72,85%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>119275</t>
+          <t>117861</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>158985</t>
+          <t>159522</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>143132</t>
+          <t>142795</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>182757</t>
+          <t>183502</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>272836</t>
+          <t>272039</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>327752</t>
+          <t>331990</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,54%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>295161</t>
+          <t>294624</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>334871</t>
+          <t>336285</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>247473</t>
+          <t>246728</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>287098</t>
+          <t>287435</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>556624</t>
+          <t>552386</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>611540</t>
+          <t>612337</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,24%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>177744</t>
+          <t>181508</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>225239</t>
+          <t>229594</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>184683</t>
+          <t>180805</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>233129</t>
+          <t>228574</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>375809</t>
+          <t>371546</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>440636</t>
+          <t>442405</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,13%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>460698</t>
+          <t>456343</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>508193</t>
+          <t>504429</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>377126</t>
+          <t>381681</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>425572</t>
+          <t>429450</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>855557</t>
+          <t>853788</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>920384</t>
+          <t>924647</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>71,34%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>153770</t>
+          <t>152051</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>201312</t>
+          <t>199515</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>219294</t>
+          <t>216347</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>269724</t>
+          <t>268433</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>382965</t>
+          <t>385478</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>451903</t>
+          <t>455316</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,69%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>480551</t>
+          <t>482348</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>528093</t>
+          <t>529812</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>441126</t>
+          <t>442417</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>491556</t>
+          <t>494503</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>940809</t>
+          <t>937396</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1009747</t>
+          <t>1007234</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,32%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>138891</t>
+          <t>139721</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>183182</t>
+          <t>184870</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>175113</t>
+          <t>174172</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>224045</t>
+          <t>223971</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>331662</t>
+          <t>325899</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>395738</t>
+          <t>394433</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,07%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>431435</t>
+          <t>429747</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>475726</t>
+          <t>474896</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>391190</t>
+          <t>391264</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>440122</t>
+          <t>441063</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>834113</t>
+          <t>835418</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>898189</t>
+          <t>903952</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>73,5%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>71771</t>
+          <t>70969</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>107783</t>
+          <t>107198</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>104385</t>
+          <t>103268</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>145256</t>
+          <t>144338</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>187404</t>
+          <t>188590</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>239722</t>
+          <t>241121</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,53%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>320283</t>
+          <t>320868</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>356295</t>
+          <t>357097</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>302544</t>
+          <t>303462</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>343415</t>
+          <t>344532</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>636144</t>
+          <t>634745</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>688462</t>
+          <t>687276</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,47%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41833</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>70837</t>
+          <t>72352</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>77043</t>
+          <t>77078</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>113001</t>
+          <t>111210</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>128291</t>
+          <t>125198</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>172546</t>
+          <t>174272</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,25%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>238949</t>
+          <t>237434</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>267953</t>
+          <t>266593</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>240995</t>
+          <t>242786</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>276953</t>
+          <t>276918</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>491236</t>
+          <t>489510</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>535491</t>
+          <t>538584</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>81,14%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14944</t>
+          <t>15190</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32995</t>
+          <t>32925</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37581</t>
+          <t>39087</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>65078</t>
+          <t>66532</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>56175</t>
+          <t>57429</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>89943</t>
+          <t>89672</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>216856</t>
+          <t>216926</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>234907</t>
+          <t>234661</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>323901</t>
+          <t>322447</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>351398</t>
+          <t>349892</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>548887</t>
+          <t>549158</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>582655</t>
+          <t>581401</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,01%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>795892</t>
+          <t>793953</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>897514</t>
+          <t>900175</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1018088</t>
+          <t>1019104</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1129440</t>
+          <t>1132904</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1844792</t>
+          <t>1846546</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1998460</t>
+          <t>2001610</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,67%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2526752</t>
+          <t>2524091</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2628374</t>
+          <t>2630313</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2427905</t>
+          <t>2424441</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2539257</t>
+          <t>2538241</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4983150</t>
+          <t>4980000</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5136818</t>
+          <t>5135064</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,55%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>141688</t>
+          <t>142870</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>181901</t>
+          <t>181647</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>156853</t>
+          <t>154977</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>193314</t>
+          <t>193618</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>307005</t>
+          <t>310292</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>364465</t>
+          <t>366577</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,97%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>237562</t>
+          <t>237816</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>277775</t>
+          <t>276593</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>202441</t>
+          <t>202137</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>238902</t>
+          <t>240778</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>450753</t>
+          <t>448641</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>508213</t>
+          <t>504926</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>61,94%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>184024</t>
+          <t>183212</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>228206</t>
+          <t>232146</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>218004</t>
+          <t>215152</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>262877</t>
+          <t>261773</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>411262</t>
+          <t>412433</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>476440</t>
+          <t>477952</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,42%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>362290</t>
+          <t>358350</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>406472</t>
+          <t>407284</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>300667</t>
+          <t>301771</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>345540</t>
+          <t>348392</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>677600</t>
+          <t>676088</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>742778</t>
+          <t>741607</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,26%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>168485</t>
+          <t>167499</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>214919</t>
+          <t>216022</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>214160</t>
+          <t>214847</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>262071</t>
+          <t>263882</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>392893</t>
+          <t>398304</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>462883</t>
+          <t>465296</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,97%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>454178</t>
+          <t>453075</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>500612</t>
+          <t>501598</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>399315</t>
+          <t>397504</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>447226</t>
+          <t>446539</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>867600</t>
+          <t>865187</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>937590</t>
+          <t>932179</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,06%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>171272</t>
+          <t>169790</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>217897</t>
+          <t>223148</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>210273</t>
+          <t>211274</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>260717</t>
+          <t>259220</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>394747</t>
+          <t>394609</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>465203</t>
+          <t>465201</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>428151</t>
+          <t>422900</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>474776</t>
+          <t>476258</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>388360</t>
+          <t>389857</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>438804</t>
+          <t>437803</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>829922</t>
+          <t>829924</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>900378</t>
+          <t>900516</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,53%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>109642</t>
+          <t>109268</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>152061</t>
+          <t>151853</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>133711</t>
+          <t>133995</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>179256</t>
+          <t>177304</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>257154</t>
+          <t>256091</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>315457</t>
+          <t>315282</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,34%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>325857</t>
+          <t>326065</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>368276</t>
+          <t>368650</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>317593</t>
+          <t>319545</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>363138</t>
+          <t>362854</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>659310</t>
+          <t>659485</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>717613</t>
+          <t>718676</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,73%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51793</t>
+          <t>52535</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>82069</t>
+          <t>81249</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>96354</t>
+          <t>96558</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>133710</t>
+          <t>133412</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>157127</t>
+          <t>155684</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>205551</t>
+          <t>202811</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,48%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252261</t>
+          <t>253081</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>282537</t>
+          <t>281795</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>244052</t>
+          <t>244350</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>281408</t>
+          <t>281204</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>506541</t>
+          <t>509281</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>554965</t>
+          <t>556408</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>78,14%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26479</t>
+          <t>26168</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46262</t>
+          <t>45365</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53664</t>
+          <t>52855</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>88207</t>
+          <t>86930</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>86613</t>
+          <t>84266</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>125988</t>
+          <t>125737</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>210736</t>
+          <t>211633</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>230519</t>
+          <t>230830</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>311962</t>
+          <t>313239</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>346505</t>
+          <t>347314</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>531179</t>
+          <t>531430</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>570554</t>
+          <t>572901</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>87,18%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>934257</t>
+          <t>939015</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1035721</t>
+          <t>1038925</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1168344</t>
+          <t>1167396</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1281496</t>
+          <t>1283111</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2131619</t>
+          <t>2129771</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2290065</t>
+          <t>2289983</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2358629</t>
+          <t>2355425</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2460093</t>
+          <t>2455335</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2263046</t>
+          <t>2261431</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2376198</t>
+          <t>2377146</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4648827</t>
+          <t>4648909</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4807273</t>
+          <t>4809121</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,31%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>111031</t>
+          <t>110207</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>84285</t>
+          <t>84483</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>145853</t>
+          <t>141473</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>100805</t>
+          <t>112321</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>79934</t>
+          <t>88867</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>122147</t>
+          <t>137383</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>211836</t>
+          <t>222528</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>175642</t>
+          <t>187305</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>253459</t>
+          <t>261149</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>34,23%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>283451</t>
+          <t>292349</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>248629</t>
+          <t>261083</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>310197</t>
+          <t>318073</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>210167</t>
+          <t>247967</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>188825</t>
+          <t>222905</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>231038</t>
+          <t>271421</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>493618</t>
+          <t>540316</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>451995</t>
+          <t>501695</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>529812</t>
+          <t>575539</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,45%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>394482</t>
+          <t>402556</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>394482</t>
+          <t>402556</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>394482</t>
+          <t>402556</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>310972</t>
+          <t>360288</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>310972</t>
+          <t>360288</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>310972</t>
+          <t>360288</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>705454</t>
+          <t>762844</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>705454</t>
+          <t>762844</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>705454</t>
+          <t>762844</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>130255</t>
+          <t>134394</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>108519</t>
+          <t>109572</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>153498</t>
+          <t>162605</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>151201</t>
+          <t>162496</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>96531</t>
+          <t>140475</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>184686</t>
+          <t>185898</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>281456</t>
+          <t>296890</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>212455</t>
+          <t>264799</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>320732</t>
+          <t>330292</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,01%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>291671</t>
+          <t>340676</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>268428</t>
+          <t>312465</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>313407</t>
+          <t>365498</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>357598</t>
+          <t>333588</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>324113</t>
+          <t>310186</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>412268</t>
+          <t>355609</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>649269</t>
+          <t>674264</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>609993</t>
+          <t>640862</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>718270</t>
+          <t>706355</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>72,73%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>421926</t>
+          <t>475070</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>421926</t>
+          <t>475070</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>421926</t>
+          <t>475070</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>508799</t>
+          <t>496084</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>508799</t>
+          <t>496084</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>508799</t>
+          <t>496084</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>930725</t>
+          <t>971154</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>930725</t>
+          <t>971154</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>930725</t>
+          <t>971154</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>148397</t>
+          <t>163656</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>128607</t>
+          <t>141158</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>171697</t>
+          <t>189562</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>210974</t>
+          <t>236163</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>193505</t>
+          <t>216313</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>230848</t>
+          <t>258090</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>359371</t>
+          <t>399819</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>329916</t>
+          <t>371376</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>388145</t>
+          <t>434139</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>35,13%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>385582</t>
+          <t>453750</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>362282</t>
+          <t>427844</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>405372</t>
+          <t>476248</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>328452</t>
+          <t>382263</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>308578</t>
+          <t>360336</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>345921</t>
+          <t>402113</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>714034</t>
+          <t>836013</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>685260</t>
+          <t>801693</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>743489</t>
+          <t>864456</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,95%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>533979</t>
+          <t>617406</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>533979</t>
+          <t>617406</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>533979</t>
+          <t>617406</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>539426</t>
+          <t>618426</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>539426</t>
+          <t>618426</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>539426</t>
+          <t>618426</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1073405</t>
+          <t>1235832</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1073405</t>
+          <t>1235832</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1073405</t>
+          <t>1235832</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>190037</t>
+          <t>204288</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82317</t>
+          <t>179486</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>275421</t>
+          <t>228393</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>274643</t>
+          <t>257937</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>245854</t>
+          <t>237634</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>340948</t>
+          <t>278899</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>464679</t>
+          <t>462224</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>289318</t>
+          <t>430364</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>568572</t>
+          <t>496651</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>34,75%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>695667</t>
+          <t>494087</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>610283</t>
+          <t>469982</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>803387</t>
+          <t>518889</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>432334</t>
+          <t>472803</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>366029</t>
+          <t>451841</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>461123</t>
+          <t>493106</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1128002</t>
+          <t>966891</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1024109</t>
+          <t>932464</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1303363</t>
+          <t>998751</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>69,89%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>885704</t>
+          <t>698375</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>885704</t>
+          <t>698375</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>885704</t>
+          <t>698375</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>706977</t>
+          <t>730740</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>706977</t>
+          <t>730740</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>706977</t>
+          <t>730740</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1592681</t>
+          <t>1429115</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1592681</t>
+          <t>1429115</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1592681</t>
+          <t>1429115</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>144784</t>
+          <t>156891</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>124382</t>
+          <t>137862</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>165950</t>
+          <t>178813</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>185064</t>
+          <t>205588</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>168880</t>
+          <t>189030</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>199443</t>
+          <t>223184</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>329848</t>
+          <t>362479</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>305867</t>
+          <t>335558</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>352947</t>
+          <t>391486</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,44%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>413670</t>
+          <t>449612</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>392504</t>
+          <t>427690</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>434072</t>
+          <t>468641</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>353595</t>
+          <t>394672</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>339216</t>
+          <t>377076</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>369779</t>
+          <t>411230</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>767265</t>
+          <t>844283</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>744166</t>
+          <t>815276</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>791246</t>
+          <t>871204</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,19%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>558454</t>
+          <t>606503</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>558454</t>
+          <t>606503</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>558454</t>
+          <t>606503</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>538659</t>
+          <t>600260</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>538659</t>
+          <t>600260</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>538659</t>
+          <t>600260</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1097113</t>
+          <t>1206762</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1097113</t>
+          <t>1206762</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1097113</t>
+          <t>1206762</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>96848</t>
+          <t>106944</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>83495</t>
+          <t>91085</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>111289</t>
+          <t>122516</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>103984</t>
+          <t>114144</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41146</t>
+          <t>101516</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>162682</t>
+          <t>127673</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>200832</t>
+          <t>221089</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>102907</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>261379</t>
+          <t>240086</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>28,62%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>265785</t>
+          <t>294016</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>251344</t>
+          <t>278444</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>279138</t>
+          <t>309875</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>503638</t>
+          <t>323763</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>444940</t>
+          <t>310234</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>566476</t>
+          <t>336391</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>769423</t>
+          <t>617778</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>708876</t>
+          <t>598781</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>867348</t>
+          <t>638271</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>76,09%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>362633</t>
+          <t>400960</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>362633</t>
+          <t>400960</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>362633</t>
+          <t>400960</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607622</t>
+          <t>437907</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607622</t>
+          <t>437907</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607622</t>
+          <t>437907</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>970255</t>
+          <t>838867</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>970255</t>
+          <t>838867</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>970255</t>
+          <t>838867</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>41361</t>
+          <t>46733</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32706</t>
+          <t>36915</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51342</t>
+          <t>58807</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>57563</t>
+          <t>63282</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48322</t>
+          <t>52965</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>69260</t>
+          <t>74992</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>98925</t>
+          <t>110016</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>85855</t>
+          <t>95016</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>113478</t>
+          <t>125760</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>237993</t>
+          <t>259251</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>228012</t>
+          <t>247177</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>246648</t>
+          <t>269069</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>359796</t>
+          <t>392082</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>348099</t>
+          <t>380372</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>369037</t>
+          <t>402399</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>597788</t>
+          <t>651332</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>583235</t>
+          <t>635588</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>610858</t>
+          <t>666332</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,52%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>279354</t>
+          <t>305984</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>279354</t>
+          <t>305984</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>279354</t>
+          <t>305984</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>417359</t>
+          <t>455364</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>417359</t>
+          <t>455364</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>417359</t>
+          <t>455364</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>696713</t>
+          <t>761348</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>696713</t>
+          <t>761348</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>696713</t>
+          <t>761348</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>862713</t>
+          <t>923114</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>669893</t>
+          <t>865964</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>947806</t>
+          <t>978975</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1084234</t>
+          <t>1151931</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>884215</t>
+          <t>1105992</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1187018</t>
+          <t>1205191</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1946946</t>
+          <t>2075045</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1673995</t>
+          <t>1999274</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2093062</t>
+          <t>2152988</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,88%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2573819</t>
+          <t>2583741</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2488726</t>
+          <t>2527880</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2766639</t>
+          <t>2640891</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2545580</t>
+          <t>2547137</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2442796</t>
+          <t>2493877</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2745599</t>
+          <t>2593076</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5119400</t>
+          <t>5130878</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4973284</t>
+          <t>5052935</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5392351</t>
+          <t>5206649</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>72,26%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3436532</t>
+          <t>3506855</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3436532</t>
+          <t>3506855</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3436532</t>
+          <t>3506855</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3629814</t>
+          <t>3699068</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3629814</t>
+          <t>3699068</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3629814</t>
+          <t>3699068</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7066346</t>
+          <t>7205923</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7066346</t>
+          <t>7205923</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7066346</t>
+          <t>7205923</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
